--- a/data/channel_priority.xlsx
+++ b/data/channel_priority.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB39F64-74E2-45B6-87ED-6F02BC46696E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4500873E-9099-41A9-AD06-EA12322D018F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kanal-prioritering" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="570">
   <si>
     <t>Kanal</t>
   </si>
@@ -1789,14 +1789,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2537,7 +2536,7 @@
       <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" t="s">
         <v>39</v>
       </c>
       <c r="D22">
@@ -2686,9 +2685,6 @@
       <c r="E29">
         <v>100</v>
       </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -2766,9 +2762,6 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -2786,9 +2779,6 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -2806,9 +2796,6 @@
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -2826,9 +2813,6 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -2846,9 +2830,6 @@
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -2866,9 +2847,6 @@
       <c r="E38">
         <v>3.5</v>
       </c>
-      <c r="F38" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -2886,9 +2864,6 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -2906,9 +2881,6 @@
       <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -2926,9 +2898,6 @@
       <c r="E41">
         <v>0</v>
       </c>
-      <c r="F41" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -2946,9 +2915,6 @@
       <c r="E42">
         <v>3.7</v>
       </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -2966,9 +2932,6 @@
       <c r="E43">
         <v>0</v>
       </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -2986,9 +2949,6 @@
       <c r="E44">
         <v>2.7</v>
       </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -3026,9 +2986,6 @@
       <c r="E46">
         <v>0</v>
       </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -3046,9 +3003,6 @@
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -3066,9 +3020,6 @@
       <c r="E48">
         <v>0</v>
       </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -3106,9 +3057,6 @@
       <c r="E50">
         <v>8.9</v>
       </c>
-      <c r="F50" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -3126,9 +3074,6 @@
       <c r="E51">
         <v>0</v>
       </c>
-      <c r="F51" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -3146,9 +3091,6 @@
       <c r="E52">
         <v>0</v>
       </c>
-      <c r="F52" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -3166,9 +3108,6 @@
       <c r="E53">
         <v>0</v>
       </c>
-      <c r="F53" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -3186,9 +3125,6 @@
       <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -3206,9 +3142,6 @@
       <c r="E55">
         <v>0</v>
       </c>
-      <c r="F55" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -3226,9 +3159,6 @@
       <c r="E56">
         <v>0</v>
       </c>
-      <c r="F56" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -3245,9 +3175,6 @@
       </c>
       <c r="E57">
         <v>35.799999999999997</v>
-      </c>
-      <c r="F57" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/channel_priority.xlsx
+++ b/data/channel_priority.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1AD3EE-82B4-4ABD-A937-A56410A2E394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31DC63E-2AC2-42AD-8AF6-3B2B9557E1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kanal-prioritering" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="191">
   <si>
     <t>Kanal</t>
   </si>
@@ -59,15 +59,6 @@
     <t>nickelodeon</t>
   </si>
   <si>
-    <t>MTV.dk</t>
-  </si>
-  <si>
-    <t>mtv</t>
-  </si>
-  <si>
-    <t>MTV (Nordic) (T).dk, MTV Denmark (DK,DA).dk, MTV.dk</t>
-  </si>
-  <si>
     <t>Nick Jr.dk</t>
   </si>
   <si>
@@ -233,12 +224,6 @@
     <t>vseries</t>
   </si>
   <si>
-    <t>ID.dk</t>
-  </si>
-  <si>
-    <t>investigationdiscovery</t>
-  </si>
-  <si>
     <t>TV3 Sport.dk</t>
   </si>
   <si>
@@ -263,30 +248,12 @@
     <t>skyshowtime1</t>
   </si>
   <si>
-    <t>Viasat Explorer.dk</t>
-  </si>
-  <si>
-    <t>viasatexplorer</t>
-  </si>
-  <si>
-    <t>Viasat Explorer.dk, viasatexplorer.dk</t>
-  </si>
-  <si>
     <t>TV2 Sport X.dk</t>
   </si>
   <si>
     <t>tv2sportx</t>
   </si>
   <si>
-    <t>History.dk</t>
-  </si>
-  <si>
-    <t>history</t>
-  </si>
-  <si>
-    <t>History Channel Denmark (DK,DA).dk, History.dk</t>
-  </si>
-  <si>
     <t>Kosmopol (Digital).dk</t>
   </si>
   <si>
@@ -311,12 +278,6 @@
     <t>skynewsinternational</t>
   </si>
   <si>
-    <t>Sky News.dk</t>
-  </si>
-  <si>
-    <t>skynews</t>
-  </si>
-  <si>
     <t>C More Stars.dk</t>
   </si>
   <si>
@@ -368,15 +329,6 @@
     <t>tv2sport</t>
   </si>
   <si>
-    <t>SPORT LIVE.dk</t>
-  </si>
-  <si>
-    <t>sportlive</t>
-  </si>
-  <si>
-    <t>Sport Live (D) (T).dk, sportlive.dk</t>
-  </si>
-  <si>
     <t>TV2 Kosmopol.dk</t>
   </si>
   <si>
@@ -410,18 +362,6 @@
     <t>sf-kanalen</t>
   </si>
   <si>
-    <t>Love Nature HD (T).dk</t>
-  </si>
-  <si>
-    <t>lovenature</t>
-  </si>
-  <si>
-    <t>Viasat Film.dk</t>
-  </si>
-  <si>
-    <t>viasatfilm</t>
-  </si>
-  <si>
     <t>ID Investigation Discovery (D) (T).dk</t>
   </si>
   <si>
@@ -449,12 +389,6 @@
     <t>vsportultra</t>
   </si>
   <si>
-    <t>Viasat Ultra.dk</t>
-  </si>
-  <si>
-    <t>viasatultra</t>
-  </si>
-  <si>
     <t>Sådan bruger du denne fil</t>
   </si>
   <si>
@@ -491,9 +425,6 @@
     <t>BBC News (T).dk, BBC News.dk, BBC.News.dk</t>
   </si>
   <si>
-    <t>ID.dk, Investigation Discovery Denmark (DK,DA).dk, Investigation Discovery.dk, Investigation.Discovery.dk</t>
-  </si>
-  <si>
     <t>Kosmopol (Digital).dk, Kosmopol.dk</t>
   </si>
   <si>
@@ -587,9 +518,6 @@
     <t>Eurosport.2.dk, EuroSport.2.HD.dk</t>
   </si>
   <si>
-    <t>ID Investigation Discovery (D) (T).dk, Investigation.Discovery.dk</t>
-  </si>
-  <si>
     <t>Kanal 4 Denmark (DK,DA).dk, Kanal 4 HD (D) (T).dk, Kanal 4.dk, kanal4.dk, Kanal.4.dk, Kanal.4.dk</t>
   </si>
   <si>
@@ -663,6 +591,12 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>ID Investigation Discovery (D) (T).dk, Investigation.Discovery.dk, ID.dk, Investigation Discovery Denmark (DK,DA).dk, Investigation Discovery.dk, Investigation.Discovery.dk</t>
+  </si>
+  <si>
+    <t>Sky News International (GB,EN).dk, Sky News.dk</t>
   </si>
 </sst>
 </file>
@@ -1037,16 +971,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="60.28515625" customWidth="1"/>
-    <col min="2" max="2" width="45.85546875" customWidth="1"/>
+    <col min="1" max="1" width="60.26953125" customWidth="1"/>
+    <col min="2" max="2" width="45.81640625" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1060,128 +994,128 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1195,80 +1129,80 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1276,682 +1210,670 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>169</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" t="s">
+        <v>175</v>
+      </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>171</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>176</v>
+      </c>
+      <c r="D47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" t="s">
         <v>181</v>
       </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>180</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
         <v>182</v>
       </c>
-      <c r="B19" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" t="s">
-        <v>182</v>
-      </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>183</v>
-      </c>
-      <c r="B20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>156</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" t="s">
-        <v>191</v>
-      </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" t="s">
-        <v>192</v>
-      </c>
-      <c r="D34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" t="s">
-        <v>210</v>
-      </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" t="s">
-        <v>93</v>
-      </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D41" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" t="s">
-        <v>159</v>
-      </c>
-      <c r="D43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>116</v>
       </c>
-      <c r="D44" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>198</v>
-      </c>
-      <c r="D47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B61" t="s">
         <v>117</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C61" t="s">
         <v>118</v>
       </c>
-      <c r="C48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" t="s">
-        <v>199</v>
-      </c>
-      <c r="D49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" t="s">
-        <v>201</v>
-      </c>
-      <c r="D50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D51" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" t="s">
-        <v>195</v>
-      </c>
-      <c r="D52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" t="s">
-        <v>200</v>
-      </c>
-      <c r="D53" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" t="s">
-        <v>72</v>
-      </c>
-      <c r="C56" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" t="s">
-        <v>135</v>
-      </c>
-      <c r="C59" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" t="s">
-        <v>103</v>
-      </c>
-      <c r="C60" t="s">
-        <v>202</v>
-      </c>
-      <c r="D60" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" t="s">
-        <v>203</v>
-      </c>
       <c r="D61" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>106</v>
       </c>
@@ -1959,142 +1881,10 @@
         <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>110</v>
-      </c>
-      <c r="B63" t="s">
-        <v>111</v>
-      </c>
-      <c r="C63" t="s">
-        <v>205</v>
-      </c>
-      <c r="D63" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" t="s">
-        <v>207</v>
-      </c>
-      <c r="D64" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>139</v>
-      </c>
-      <c r="B65" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" t="s">
-        <v>166</v>
-      </c>
-      <c r="D65" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>124</v>
-      </c>
-      <c r="B66" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" t="s">
-        <v>206</v>
-      </c>
-      <c r="D66" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" t="s">
-        <v>80</v>
-      </c>
-      <c r="C67" t="s">
-        <v>81</v>
-      </c>
-      <c r="D67" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" t="s">
-        <v>138</v>
-      </c>
-      <c r="D68" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>130</v>
-      </c>
-      <c r="B69" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69" t="s">
-        <v>130</v>
-      </c>
-      <c r="D69" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>122</v>
-      </c>
-      <c r="B70" t="s">
-        <v>123</v>
-      </c>
-      <c r="C70" t="s">
-        <v>208</v>
-      </c>
-      <c r="D70" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>141</v>
-      </c>
-      <c r="B71" t="s">
-        <v>142</v>
-      </c>
-      <c r="C71" t="s">
-        <v>141</v>
-      </c>
-      <c r="D71" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" t="s">
-        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2104,7 +1894,7 @@
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D68" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D61" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2116,69 +1906,69 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
